--- a/input/timetable/Магистратура_Химия.xlsx
+++ b/input/timetable/Магистратура_Химия.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
   <si>
     <t>пара</t>
   </si>
@@ -165,6 +165,9 @@
   </si>
   <si>
     <t>Нефтепромысловая химия (лаб), А131</t>
+  </si>
+  <si>
+    <t>День самостоятельной работы</t>
   </si>
 </sst>
 </file>
@@ -732,7 +735,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="91">
+  <cellXfs count="88">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -841,46 +844,6 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
@@ -918,6 +881,15 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -946,6 +918,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1384,10 +1378,10 @@
       <c r="A9" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="C9" s="45" t="s">
+      <c r="C9" s="81" t="s">
         <v>42</v>
       </c>
-      <c r="D9" s="45"/>
+      <c r="D9" s="81"/>
       <c r="E9" s="38"/>
     </row>
     <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
@@ -1411,32 +1405,32 @@
       <c r="B11" s="21">
         <v>6</v>
       </c>
-      <c r="C11" s="67"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="69"/>
+      <c r="C11" s="51"/>
+      <c r="D11" s="52"/>
+      <c r="E11" s="52"/>
+      <c r="F11" s="53"/>
     </row>
     <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="22"/>
       <c r="B12" s="23">
         <v>7</v>
       </c>
-      <c r="C12" s="70" t="s">
+      <c r="C12" s="54" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="71"/>
-      <c r="E12" s="71"/>
-      <c r="F12" s="72"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="56"/>
     </row>
     <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A13" s="24"/>
       <c r="B13" s="25">
         <v>8</v>
       </c>
-      <c r="C13" s="73"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="75"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="59"/>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A14" s="26" t="s">
@@ -1445,34 +1439,34 @@
       <c r="B14" s="21">
         <v>6</v>
       </c>
-      <c r="C14" s="76"/>
-      <c r="D14" s="77"/>
-      <c r="E14" s="77"/>
-      <c r="F14" s="78"/>
+      <c r="C14" s="60"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
+      <c r="F14" s="62"/>
     </row>
     <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="22"/>
       <c r="B15" s="23">
         <v>7</v>
       </c>
-      <c r="C15" s="49" t="s">
+      <c r="C15" s="63" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="50"/>
-      <c r="E15" s="50"/>
-      <c r="F15" s="51"/>
+      <c r="D15" s="64"/>
+      <c r="E15" s="64"/>
+      <c r="F15" s="65"/>
     </row>
     <row r="16" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A16" s="27"/>
       <c r="B16" s="25">
         <v>8</v>
       </c>
-      <c r="C16" s="79" t="s">
+      <c r="C16" s="66" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="80"/>
-      <c r="E16" s="80"/>
-      <c r="F16" s="81"/>
+      <c r="D16" s="67"/>
+      <c r="E16" s="67"/>
+      <c r="F16" s="68"/>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" s="26" t="s">
@@ -1481,34 +1475,34 @@
       <c r="B17" s="21">
         <v>6</v>
       </c>
-      <c r="C17" s="82"/>
-      <c r="D17" s="83"/>
-      <c r="E17" s="83"/>
-      <c r="F17" s="84"/>
+      <c r="C17" s="69"/>
+      <c r="D17" s="70"/>
+      <c r="E17" s="70"/>
+      <c r="F17" s="71"/>
     </row>
     <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A18" s="22"/>
       <c r="B18" s="23">
         <v>7</v>
       </c>
-      <c r="C18" s="49" t="s">
+      <c r="C18" s="63" t="s">
         <v>43</v>
       </c>
-      <c r="D18" s="50"/>
-      <c r="E18" s="50"/>
-      <c r="F18" s="51"/>
+      <c r="D18" s="64"/>
+      <c r="E18" s="64"/>
+      <c r="F18" s="65"/>
     </row>
     <row r="19" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A19" s="27"/>
       <c r="B19" s="25">
         <v>8</v>
       </c>
-      <c r="C19" s="85" t="s">
+      <c r="C19" s="72" t="s">
         <v>44</v>
       </c>
-      <c r="D19" s="86"/>
-      <c r="E19" s="86"/>
-      <c r="F19" s="87"/>
+      <c r="D19" s="73"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="74"/>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" s="26" t="s">
@@ -1517,34 +1511,34 @@
       <c r="B20" s="21">
         <v>6</v>
       </c>
-      <c r="C20" s="88"/>
-      <c r="D20" s="89"/>
-      <c r="E20" s="89"/>
-      <c r="F20" s="90"/>
+      <c r="C20" s="75"/>
+      <c r="D20" s="76"/>
+      <c r="E20" s="76"/>
+      <c r="F20" s="77"/>
     </row>
     <row r="21" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="22"/>
       <c r="B21" s="23">
         <v>7</v>
       </c>
-      <c r="C21" s="49" t="s">
+      <c r="C21" s="63" t="s">
         <v>35</v>
       </c>
-      <c r="D21" s="50"/>
-      <c r="E21" s="50"/>
-      <c r="F21" s="51"/>
+      <c r="D21" s="64"/>
+      <c r="E21" s="64"/>
+      <c r="F21" s="65"/>
     </row>
     <row r="22" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A22" s="27"/>
       <c r="B22" s="25">
         <v>8</v>
       </c>
-      <c r="C22" s="85" t="s">
+      <c r="C22" s="72" t="s">
         <v>35</v>
       </c>
-      <c r="D22" s="86"/>
-      <c r="E22" s="86"/>
-      <c r="F22" s="87"/>
+      <c r="D22" s="73"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="74"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" s="26" t="s">
@@ -1553,34 +1547,32 @@
       <c r="B23" s="21">
         <v>6</v>
       </c>
-      <c r="C23" s="82"/>
-      <c r="D23" s="83"/>
-      <c r="E23" s="83"/>
-      <c r="F23" s="84"/>
+      <c r="C23" s="78" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="79"/>
+      <c r="E23" s="79"/>
+      <c r="F23" s="80"/>
     </row>
     <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="28"/>
       <c r="B24" s="23">
         <v>7</v>
       </c>
-      <c r="C24" s="49" t="s">
-        <v>45</v>
-      </c>
-      <c r="D24" s="50"/>
-      <c r="E24" s="50"/>
-      <c r="F24" s="51"/>
+      <c r="C24" s="63"/>
+      <c r="D24" s="64"/>
+      <c r="E24" s="64"/>
+      <c r="F24" s="65"/>
     </row>
     <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A25" s="29"/>
       <c r="B25" s="25">
         <v>8</v>
       </c>
-      <c r="C25" s="64" t="s">
-        <v>45</v>
-      </c>
-      <c r="D25" s="65"/>
-      <c r="E25" s="65"/>
-      <c r="F25" s="66"/>
+      <c r="C25" s="48"/>
+      <c r="D25" s="49"/>
+      <c r="E25" s="49"/>
+      <c r="F25" s="50"/>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" s="39" t="s">
@@ -1589,76 +1581,80 @@
       <c r="B26" s="32">
         <v>1</v>
       </c>
-      <c r="C26" s="46" t="s">
+      <c r="C26" s="78" t="s">
         <v>46</v>
       </c>
-      <c r="D26" s="47"/>
-      <c r="E26" s="47"/>
-      <c r="F26" s="48"/>
+      <c r="D26" s="79"/>
+      <c r="E26" s="79"/>
+      <c r="F26" s="80"/>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" s="30"/>
       <c r="B27" s="23">
         <v>2</v>
       </c>
-      <c r="C27" s="49" t="s">
+      <c r="C27" s="63" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="50"/>
-      <c r="E27" s="50"/>
-      <c r="F27" s="51"/>
+      <c r="D27" s="64"/>
+      <c r="E27" s="64"/>
+      <c r="F27" s="65"/>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" s="43"/>
       <c r="B28" s="44">
         <v>4</v>
       </c>
-      <c r="C28" s="52"/>
-      <c r="D28" s="53"/>
-      <c r="E28" s="53"/>
-      <c r="F28" s="54"/>
+      <c r="C28" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D28" s="64"/>
+      <c r="E28" s="64"/>
+      <c r="F28" s="65"/>
     </row>
     <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A29" s="40"/>
       <c r="B29" s="25">
         <v>5</v>
       </c>
-      <c r="C29" s="52"/>
-      <c r="D29" s="53"/>
-      <c r="E29" s="53"/>
-      <c r="F29" s="54"/>
+      <c r="C29" s="63" t="s">
+        <v>45</v>
+      </c>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="65"/>
     </row>
     <row r="30" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A30" s="41"/>
       <c r="B30" s="42"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="59"/>
-      <c r="E30" s="59"/>
-      <c r="F30" s="60"/>
+      <c r="C30" s="85"/>
+      <c r="D30" s="86"/>
+      <c r="E30" s="86"/>
+      <c r="F30" s="87"/>
     </row>
     <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A31" s="31"/>
       <c r="B31" s="32" t="s">
         <v>28</v>
       </c>
-      <c r="C31" s="55" t="s">
+      <c r="C31" s="82" t="s">
         <v>29</v>
       </c>
-      <c r="D31" s="56"/>
-      <c r="E31" s="56"/>
-      <c r="F31" s="57"/>
+      <c r="D31" s="83"/>
+      <c r="E31" s="83"/>
+      <c r="F31" s="84"/>
     </row>
     <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A32" s="33"/>
       <c r="B32" s="25" t="s">
         <v>28</v>
       </c>
-      <c r="C32" s="61" t="s">
+      <c r="C32" s="45" t="s">
         <v>30</v>
       </c>
-      <c r="D32" s="62"/>
-      <c r="E32" s="62"/>
-      <c r="F32" s="63"/>
+      <c r="D32" s="46"/>
+      <c r="E32" s="46"/>
+      <c r="F32" s="47"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
@@ -1678,6 +1674,13 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C11:F11"/>
@@ -1694,13 +1697,6 @@
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>

--- a/input/timetable/Магистратура_Химия.xlsx
+++ b/input/timetable/Магистратура_Химия.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="58">
   <si>
     <t>пара</t>
   </si>
@@ -62,6 +62,9 @@
     <t>Директор института</t>
   </si>
   <si>
+    <t>Преподаватель</t>
+  </si>
+  <si>
     <t>Направление</t>
   </si>
   <si>
@@ -116,18 +119,27 @@
     <t>Самоорганизация и саморазвитие (лек 16 ч)</t>
   </si>
   <si>
+    <t>Кокорина К.А.</t>
+  </si>
+  <si>
     <t>Производственная практика, научно-исследовательская работа, ЭОиДОТ//</t>
   </si>
   <si>
     <t>Научно-исследовательский семинар (пр), ЭОиДОТ//</t>
   </si>
   <si>
+    <t>Францина Е.В.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Зав.кафедрой </t>
   </si>
   <si>
     <t>Самоорганизация и саморазвитие  (пр), ЭОиДОТ//Лидерство и командная работа при разработке и реализации проектов (пр), ЭОиДОТ</t>
   </si>
   <si>
+    <t>Нехорошев В.П.</t>
+  </si>
+  <si>
     <t>Нефтепромысловая химия (лек), ЭОиДОТ//</t>
   </si>
   <si>
@@ -137,6 +149,9 @@
     <t xml:space="preserve">               РАСПИСАНИЕ УЧЕБНЫХ ЗАНЯТИЙ </t>
   </si>
   <si>
+    <t>Закирова К.Р.</t>
+  </si>
+  <si>
     <t>2025-2026</t>
   </si>
   <si>
@@ -152,10 +167,22 @@
     <t>02.02.2026- 06.06.2026</t>
   </si>
   <si>
+    <t>Усаева Н.Р.</t>
+  </si>
+  <si>
+    <t>Усаева Н.Р./Лукиянчина Е.В.</t>
+  </si>
+  <si>
+    <t>Лукиянчина Е.В.</t>
+  </si>
+  <si>
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ// ФТД: Иностранный язык (лек), ЭОиДОТ</t>
   </si>
   <si>
     <t>Практикум по межкультурной коммуникации (пр), ЭОиДОТ// ФТД: Иностранный язык (пр), ЭОиДОТ</t>
+  </si>
+  <si>
+    <t>Малагин Д.В./Джумаева А.А.</t>
   </si>
   <si>
     <t xml:space="preserve"> Химия нефти и газа (лек), ЭОиДОТ//</t>
@@ -268,7 +295,7 @@
       <charset val="204"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -287,12 +314,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.14999847407452621"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="40">
     <border>
       <left/>
       <right/>
@@ -372,6 +405,64 @@
       <diagonal/>
     </border>
     <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color indexed="64"/>
       </left>
@@ -667,6 +758,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
       <left style="medium">
         <color indexed="64"/>
       </left>
@@ -721,6 +821,19 @@
         <color indexed="64"/>
       </left>
       <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -735,7 +848,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="98">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -768,28 +881,31 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="11" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="centerContinuous"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="15" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -807,6 +923,7 @@
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
@@ -818,7 +935,7 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
@@ -837,109 +954,117 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="2" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="26" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="30" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1271,7 +1396,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.85546875" style="2" customWidth="1"/>
@@ -1280,10 +1405,11 @@
     <col min="4" max="4" width="20.28515625" style="2" customWidth="1"/>
     <col min="5" max="5" width="19.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="19.7109375" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9.140625" style="2"/>
+    <col min="7" max="7" width="18.140625" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>7</v>
       </c>
@@ -1291,15 +1417,15 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="F2" s="3" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
         <v>10</v>
       </c>
@@ -1307,86 +1433,86 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="4" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B4" s="5"/>
       <c r="C4" s="5"/>
       <c r="D4" s="6"/>
       <c r="E4" s="5"/>
       <c r="F4" s="7" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.4">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="8" t="s">
         <v>2</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="D5" s="9"/>
       <c r="E5" s="10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="34" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="34"/>
-      <c r="E6" s="35">
+      <c r="C6" s="36" t="s">
+        <v>15</v>
+      </c>
+      <c r="D6" s="36"/>
+      <c r="E6" s="37">
         <v>1</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="12" t="s">
-        <v>13</v>
-      </c>
-      <c r="C7" s="36" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="36"/>
-      <c r="E7" s="37" t="s">
-        <v>40</v>
+        <v>14</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>17</v>
+      </c>
+      <c r="D7" s="38"/>
+      <c r="E7" s="39" t="s">
+        <v>45</v>
       </c>
       <c r="F7" s="13" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="C8" s="34" t="s">
         <v>25</v>
       </c>
-      <c r="D8" s="38"/>
-      <c r="E8" s="38"/>
-    </row>
-    <row r="9" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="C8" s="36" t="s">
+        <v>26</v>
+      </c>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+    </row>
+    <row r="9" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A9" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C9" s="81" t="s">
-        <v>42</v>
-      </c>
-      <c r="D9" s="81"/>
-      <c r="E9" s="38"/>
-    </row>
-    <row r="10" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+        <v>28</v>
+      </c>
+      <c r="C9" s="55" t="s">
+        <v>47</v>
+      </c>
+      <c r="D9" s="55"/>
+      <c r="E9" s="40"/>
+    </row>
+    <row r="10" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="A10" s="14" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B10" s="15" t="s">
         <v>0</v>
@@ -1397,290 +1523,334 @@
       <c r="D10" s="17"/>
       <c r="E10" s="18"/>
       <c r="F10" s="19"/>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A11" s="20" t="s">
-        <v>18</v>
-      </c>
-      <c r="B11" s="21">
+      <c r="G10" s="20" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A11" s="21" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="22">
         <v>6</v>
       </c>
-      <c r="C11" s="51"/>
-      <c r="D11" s="52"/>
-      <c r="E11" s="52"/>
-      <c r="F11" s="53"/>
-    </row>
-    <row r="12" spans="1:6" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="22"/>
-      <c r="B12" s="23">
+      <c r="C11" s="74"/>
+      <c r="D11" s="75"/>
+      <c r="E11" s="75"/>
+      <c r="F11" s="76"/>
+      <c r="G11" s="28"/>
+    </row>
+    <row r="12" spans="1:7" ht="39.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="23"/>
+      <c r="B12" s="24">
         <v>7</v>
       </c>
-      <c r="C12" s="54" t="s">
+      <c r="C12" s="77" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="78"/>
+      <c r="E12" s="78"/>
+      <c r="F12" s="79"/>
+      <c r="G12" s="50" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="25"/>
+      <c r="B13" s="26">
+        <v>8</v>
+      </c>
+      <c r="C13" s="80"/>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="82"/>
+      <c r="G13" s="48"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A14" s="27" t="s">
+        <v>20</v>
+      </c>
+      <c r="B14" s="22">
+        <v>6</v>
+      </c>
+      <c r="C14" s="83"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="28"/>
+    </row>
+    <row r="15" spans="1:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="23"/>
+      <c r="B15" s="24">
+        <v>7</v>
+      </c>
+      <c r="C15" s="59" t="s">
         <v>34</v>
       </c>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="56"/>
-    </row>
-    <row r="13" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A13" s="24"/>
-      <c r="B13" s="25">
+      <c r="D15" s="60"/>
+      <c r="E15" s="60"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="50" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="29"/>
+      <c r="B16" s="26">
         <v>8</v>
       </c>
-      <c r="C13" s="57"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="59"/>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A14" s="26" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="21">
+      <c r="C16" s="86" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="88"/>
+      <c r="G16" s="52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A17" s="27" t="s">
+        <v>21</v>
+      </c>
+      <c r="B17" s="22">
         <v>6</v>
       </c>
-      <c r="C14" s="60"/>
-      <c r="D14" s="61"/>
-      <c r="E14" s="61"/>
-      <c r="F14" s="62"/>
-    </row>
-    <row r="15" spans="1:6" ht="18.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="22"/>
-      <c r="B15" s="23">
+      <c r="C17" s="89"/>
+      <c r="D17" s="90"/>
+      <c r="E17" s="90"/>
+      <c r="F17" s="91"/>
+      <c r="G17" s="28"/>
+    </row>
+    <row r="18" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24">
         <v>7</v>
       </c>
-      <c r="C15" s="63" t="s">
+      <c r="C18" s="59" t="s">
+        <v>51</v>
+      </c>
+      <c r="D18" s="60"/>
+      <c r="E18" s="60"/>
+      <c r="F18" s="61"/>
+      <c r="G18" s="51" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="29"/>
+      <c r="B19" s="26">
+        <v>8</v>
+      </c>
+      <c r="C19" s="92" t="s">
+        <v>52</v>
+      </c>
+      <c r="D19" s="93"/>
+      <c r="E19" s="93"/>
+      <c r="F19" s="94"/>
+      <c r="G19" s="52" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A20" s="27" t="s">
+        <v>22</v>
+      </c>
+      <c r="B20" s="22">
+        <v>6</v>
+      </c>
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="96"/>
+      <c r="F20" s="97"/>
+      <c r="G20" s="28"/>
+    </row>
+    <row r="21" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="23"/>
+      <c r="B21" s="24">
+        <v>7</v>
+      </c>
+      <c r="C21" s="59" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="60"/>
+      <c r="E21" s="60"/>
+      <c r="F21" s="61"/>
+      <c r="G21" s="50" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="65"/>
-    </row>
-    <row r="16" spans="1:6" ht="39" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A16" s="27"/>
-      <c r="B16" s="25">
+    </row>
+    <row r="22" spans="1:7" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="29"/>
+      <c r="B22" s="26">
         <v>8</v>
       </c>
-      <c r="C16" s="66" t="s">
+      <c r="C22" s="92" t="s">
+        <v>39</v>
+      </c>
+      <c r="D22" s="93"/>
+      <c r="E22" s="93"/>
+      <c r="F22" s="94"/>
+      <c r="G22" s="52" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A23" s="27" t="s">
+        <v>23</v>
+      </c>
+      <c r="B23" s="22">
+        <v>6</v>
+      </c>
+      <c r="C23" s="56" t="s">
+        <v>57</v>
+      </c>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="28"/>
+    </row>
+    <row r="24" spans="1:7" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="30"/>
+      <c r="B24" s="24">
+        <v>7</v>
+      </c>
+      <c r="C24" s="59"/>
+      <c r="D24" s="60"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="61"/>
+      <c r="G24" s="50"/>
+    </row>
+    <row r="25" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A25" s="31"/>
+      <c r="B25" s="26">
+        <v>8</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="72"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="52"/>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A26" s="41" t="s">
+        <v>24</v>
+      </c>
+      <c r="B26" s="34">
+        <v>1</v>
+      </c>
+      <c r="C26" s="56" t="s">
+        <v>55</v>
+      </c>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="54" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A27" s="32"/>
+      <c r="B27" s="24">
+        <v>2</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>56</v>
+      </c>
+      <c r="D27" s="60"/>
+      <c r="E27" s="60"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="50" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+      <c r="A28" s="46"/>
+      <c r="B28" s="47">
+        <v>4</v>
+      </c>
+      <c r="C28" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="D28" s="60"/>
+      <c r="E28" s="60"/>
+      <c r="F28" s="61"/>
+      <c r="G28" s="51" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A29" s="42"/>
+      <c r="B29" s="26">
+        <v>5</v>
+      </c>
+      <c r="C29" s="59" t="s">
+        <v>54</v>
+      </c>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="61"/>
+      <c r="G29" s="52" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="44"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="65"/>
+      <c r="D30" s="66"/>
+      <c r="E30" s="66"/>
+      <c r="F30" s="67"/>
+      <c r="G30" s="43"/>
+    </row>
+    <row r="31" spans="1:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A31" s="33"/>
+      <c r="B31" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="C31" s="62" t="s">
+        <v>30</v>
+      </c>
+      <c r="D31" s="63"/>
+      <c r="E31" s="63"/>
+      <c r="F31" s="64"/>
+      <c r="G31" s="53" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A32" s="35"/>
+      <c r="B32" s="26" t="s">
+        <v>29</v>
+      </c>
+      <c r="C32" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D16" s="67"/>
-      <c r="E16" s="67"/>
-      <c r="F16" s="68"/>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A17" s="26" t="s">
-        <v>20</v>
-      </c>
-      <c r="B17" s="21">
-        <v>6</v>
-      </c>
-      <c r="C17" s="69"/>
-      <c r="D17" s="70"/>
-      <c r="E17" s="70"/>
-      <c r="F17" s="71"/>
-    </row>
-    <row r="18" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="22"/>
-      <c r="B18" s="23">
-        <v>7</v>
-      </c>
-      <c r="C18" s="63" t="s">
-        <v>43</v>
-      </c>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
-      <c r="F18" s="65"/>
-    </row>
-    <row r="19" spans="1:6" ht="37.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A19" s="27"/>
-      <c r="B19" s="25">
-        <v>8</v>
-      </c>
-      <c r="C19" s="72" t="s">
-        <v>44</v>
-      </c>
-      <c r="D19" s="73"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="74"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A20" s="26" t="s">
-        <v>21</v>
-      </c>
-      <c r="B20" s="21">
-        <v>6</v>
-      </c>
-      <c r="C20" s="75"/>
-      <c r="D20" s="76"/>
-      <c r="E20" s="76"/>
-      <c r="F20" s="77"/>
-    </row>
-    <row r="21" spans="1:6" ht="23.25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="22"/>
-      <c r="B21" s="23">
-        <v>7</v>
-      </c>
-      <c r="C21" s="63" t="s">
-        <v>35</v>
-      </c>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="65"/>
-    </row>
-    <row r="22" spans="1:6" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A22" s="27"/>
-      <c r="B22" s="25">
-        <v>8</v>
-      </c>
-      <c r="C22" s="72" t="s">
-        <v>35</v>
-      </c>
-      <c r="D22" s="73"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="74"/>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A23" s="26" t="s">
-        <v>22</v>
-      </c>
-      <c r="B23" s="21">
-        <v>6</v>
-      </c>
-      <c r="C23" s="78" t="s">
+      <c r="D32" s="69"/>
+      <c r="E32" s="69"/>
+      <c r="F32" s="70"/>
+      <c r="G32" s="49" t="s">
         <v>48</v>
       </c>
-      <c r="D23" s="79"/>
-      <c r="E23" s="79"/>
-      <c r="F23" s="80"/>
-    </row>
-    <row r="24" spans="1:6" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="28"/>
-      <c r="B24" s="23">
-        <v>7</v>
-      </c>
-      <c r="C24" s="63"/>
-      <c r="D24" s="64"/>
-      <c r="E24" s="64"/>
-      <c r="F24" s="65"/>
-    </row>
-    <row r="25" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A25" s="29"/>
-      <c r="B25" s="25">
-        <v>8</v>
-      </c>
-      <c r="C25" s="48"/>
-      <c r="D25" s="49"/>
-      <c r="E25" s="49"/>
-      <c r="F25" s="50"/>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A26" s="39" t="s">
-        <v>23</v>
-      </c>
-      <c r="B26" s="32">
-        <v>1</v>
-      </c>
-      <c r="C26" s="78" t="s">
-        <v>46</v>
-      </c>
-      <c r="D26" s="79"/>
-      <c r="E26" s="79"/>
-      <c r="F26" s="80"/>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A27" s="30"/>
-      <c r="B27" s="23">
-        <v>2</v>
-      </c>
-      <c r="C27" s="63" t="s">
-        <v>47</v>
-      </c>
-      <c r="D27" s="64"/>
-      <c r="E27" s="64"/>
-      <c r="F27" s="65"/>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
-      <c r="A28" s="43"/>
-      <c r="B28" s="44">
-        <v>4</v>
-      </c>
-      <c r="C28" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D28" s="64"/>
-      <c r="E28" s="64"/>
-      <c r="F28" s="65"/>
-    </row>
-    <row r="29" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A29" s="40"/>
-      <c r="B29" s="25">
-        <v>5</v>
-      </c>
-      <c r="C29" s="63" t="s">
-        <v>45</v>
-      </c>
-      <c r="D29" s="64"/>
-      <c r="E29" s="64"/>
-      <c r="F29" s="65"/>
-    </row>
-    <row r="30" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A30" s="41"/>
-      <c r="B30" s="42"/>
-      <c r="C30" s="85"/>
-      <c r="D30" s="86"/>
-      <c r="E30" s="86"/>
-      <c r="F30" s="87"/>
-    </row>
-    <row r="31" spans="1:6" ht="33.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A31" s="31"/>
-      <c r="B31" s="32" t="s">
-        <v>28</v>
-      </c>
-      <c r="C31" s="82" t="s">
-        <v>29</v>
-      </c>
-      <c r="D31" s="83"/>
-      <c r="E31" s="83"/>
-      <c r="F31" s="84"/>
-    </row>
-    <row r="32" spans="1:6" ht="19.5" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A32" s="33"/>
-      <c r="B32" s="25" t="s">
-        <v>28</v>
-      </c>
-      <c r="C32" s="45" t="s">
-        <v>30</v>
-      </c>
-      <c r="D32" s="46"/>
-      <c r="E32" s="46"/>
-      <c r="F32" s="47"/>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A34" s="2" t="s">
         <v>12</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.4">
       <c r="A35" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>41</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="C26:F26"/>
-    <mergeCell ref="C27:F27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="C31:F31"/>
-    <mergeCell ref="C30:F30"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="C32:F32"/>
     <mergeCell ref="C25:F25"/>
     <mergeCell ref="C11:F11"/>
@@ -1697,6 +1867,13 @@
     <mergeCell ref="C22:F22"/>
     <mergeCell ref="C23:F23"/>
     <mergeCell ref="C24:F24"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="C26:F26"/>
+    <mergeCell ref="C27:F27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="C31:F31"/>
+    <mergeCell ref="C30:F30"/>
+    <mergeCell ref="C28:F28"/>
   </mergeCells>
   <dataValidations count="3">
     <dataValidation allowBlank="1" showDropDown="1" showInputMessage="1" showErrorMessage="1" sqref="C6"/>
